--- a/tool/kintone-aggregator/template/アラート検知.xlsx
+++ b/tool/kintone-aggregator/template/アラート検知.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-aggregator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEC660D-C9F6-41C9-B4D5-EC29DF21088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7133249C-CCDB-4714-8FEB-6C2D1940661D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23D1906F-ABF5-443E-AF8C-34868E368ECE}"/>
   </bookViews>
@@ -21,8 +21,8 @@
     <sheet name="研修スケジュール" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'提出状況-全日'!$D$3:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'提出状況-当日'!$B$6:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'提出状況-全日'!$E$3:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'提出状況-当日'!$B$6:$N$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
@@ -350,6 +350,16 @@
     <t>◆当日データ</t>
     <rPh sb="1" eb="3">
       <t>トウジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出席状況</t>
+    <rPh sb="0" eb="2">
+      <t>シュッセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -396,7 +406,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,6 +473,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -647,7 +663,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -780,9 +796,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -801,9 +814,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -868,6 +878,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1189,142 +1214,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544E91CD-F8A7-473E-9138-B816839C4C8A}">
-  <dimension ref="B1:M7"/>
+  <dimension ref="B1:N7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.69921875" customWidth="1"/>
     <col min="2" max="2" width="11.69921875" customWidth="1"/>
-    <col min="3" max="4" width="15.69921875" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.69921875" customWidth="1"/>
-    <col min="7" max="7" width="15.69921875" customWidth="1"/>
-    <col min="8" max="8" width="40.69921875" customWidth="1"/>
-    <col min="9" max="9" width="30.69921875" customWidth="1"/>
-    <col min="10" max="12" width="15.69921875" customWidth="1"/>
-    <col min="13" max="13" width="50.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="G1" s="53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B2" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="72" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="73"/>
-      <c r="G2" s="54" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="55"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B3" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="44"/>
-      <c r="G3" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="57"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="G4" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="59"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="K5" s="45"/>
-      <c r="M5" s="45"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B6" s="52" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="L6" s="47" t="s">
-        <v>6</v>
-      </c>
-      <c r="M6" s="48" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B7" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C2:D2"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870332A5-84D0-46C8-BF43-7ECC8C0CF50C}">
-  <dimension ref="B1:N4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="5.69921875" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" customWidth="1"/>
-    <col min="3" max="3" width="30.69921875" customWidth="1"/>
-    <col min="4" max="5" width="15.69921875" customWidth="1"/>
+    <col min="3" max="5" width="15.69921875" customWidth="1"/>
     <col min="6" max="6" width="10.59765625" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" customWidth="1"/>
     <col min="8" max="8" width="15.69921875" customWidth="1"/>
@@ -1336,73 +1231,218 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="H1" s="51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="72"/>
+      <c r="E2" s="71"/>
+      <c r="H2" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="53"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B3" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="75"/>
+      <c r="H3" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="55"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H4" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="57"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="L5" s="44"/>
+      <c r="N5" s="44"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B6" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B7" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{870332A5-84D0-46C8-BF43-7ECC8C0CF50C}">
+  <dimension ref="B1:O5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="5.69921875" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" customWidth="1"/>
+    <col min="3" max="3" width="30.69921875" customWidth="1"/>
+    <col min="4" max="6" width="15.69921875" customWidth="1"/>
+    <col min="7" max="7" width="10.59765625" customWidth="1"/>
+    <col min="8" max="8" width="18.69921875" customWidth="1"/>
+    <col min="9" max="9" width="15.69921875" customWidth="1"/>
+    <col min="10" max="10" width="40.69921875" customWidth="1"/>
+    <col min="11" max="11" width="30.69921875" customWidth="1"/>
+    <col min="12" max="14" width="15.69921875" customWidth="1"/>
+    <col min="15" max="15" width="50.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B1" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="C2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.45">
       <c r="F2" s="2"/>
-      <c r="L2" s="45"/>
-      <c r="N2" s="45"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B3" s="64" t="s">
+      <c r="G2" s="2"/>
+      <c r="M2" s="44"/>
+      <c r="O2" s="44"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B3" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="F3" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="G3" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="H3" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="I3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="J3" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="43" t="s">
+      <c r="K3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="L3" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="48" t="s">
+      <c r="M3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="47" t="s">
+      <c r="N3" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="48" t="s">
+      <c r="O3" s="47" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="B4" s="61" t="s">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B4" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="32"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="49"/>
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
       <c r="J4" s="32"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="49"/>
       <c r="M4" s="31"/>
       <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="D5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1435,13 +1475,13 @@
       <c r="E2" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="67"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="65"/>
       <c r="I2" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="69"/>
+      <c r="J2" s="67"/>
     </row>
     <row r="3" spans="2:10" ht="36" x14ac:dyDescent="0.45">
       <c r="B3" s="27" t="s">
@@ -1465,10 +1505,10 @@
       <c r="H3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="I3" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="65" t="s">
+      <c r="J3" s="63" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1482,8 +1522,8 @@
       <c r="F4" s="32"/>
       <c r="G4" s="32"/>
       <c r="H4" s="31"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
